--- a/assets/ESR Formations-Saxony.xlsx
+++ b/assets/ESR Formations-Saxony.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9efa18f7c2e81ea4/Documents/NewRecruit/ESR_NewRecruit/assets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9EFA18F7C2E81EA4/Documents/NewRecruit/ESR/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="8_{6A81E90A-F6D3-457A-B415-BA9F69045CE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2984671C-3B53-4AF7-89DB-607888A7E7F9}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="8_{6A81E90A-F6D3-457A-B415-BA9F69045CE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4976F383-EC85-43F2-951F-A3D9E127FBDD}"/>
   <bookViews>
-    <workbookView xWindow="585" yWindow="180" windowWidth="26610" windowHeight="14700" activeTab="1" xr2:uid="{20271C60-C4FB-4B77-A1B3-909BAACA5FD5}"/>
+    <workbookView xWindow="-27180" yWindow="975" windowWidth="26610" windowHeight="14595" activeTab="1" xr2:uid="{20271C60-C4FB-4B77-A1B3-909BAACA5FD5}"/>
   </bookViews>
   <sheets>
     <sheet name="BaselineFormations" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -139,9 +139,6 @@
     <t>Artillery zu Pferd Batterie</t>
   </si>
   <si>
-    <t>Leichtes Kavallerie-Brigade</t>
-  </si>
-  <si>
     <t>Husaren Squadron Groups</t>
   </si>
   <si>
@@ -151,9 +148,6 @@
     <t>Uhlanen Squadron Groups</t>
   </si>
   <si>
-    <t>Korps Reservieren</t>
-  </si>
-  <si>
     <t>Artillery</t>
   </si>
   <si>
@@ -166,9 +160,6 @@
     <t>Genie Sapeurs Kompagnie</t>
   </si>
   <si>
-    <t>Infanterie-Division</t>
-  </si>
-  <si>
     <t>SX Leichtes Infanterie</t>
   </si>
   <si>
@@ -203,6 +194,15 @@
   </si>
   <si>
     <t>SX Pioniere</t>
+  </si>
+  <si>
+    <t>SX Infanterie-Division</t>
+  </si>
+  <si>
+    <t>SX Leichtes Kavallerie-Brigade</t>
+  </si>
+  <si>
+    <t>SX Korps Reservieren</t>
   </si>
 </sst>
 </file>
@@ -347,17 +347,17 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -737,72 +737,72 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" s="14" t="s">
+      <c r="A2" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="11"/>
+      <c r="C2" s="14"/>
       <c r="D2" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="2">
         <v>1</v>
       </c>
-      <c r="F2" s="11"/>
+      <c r="F2" s="14"/>
       <c r="I2" s="5"/>
       <c r="J2" s="5"/>
     </row>
     <row r="3" spans="1:10" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13"/>
-      <c r="B3" s="14"/>
-      <c r="C3" s="11"/>
+      <c r="A3" s="12"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="14"/>
       <c r="D3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E3" s="2">
         <v>6</v>
       </c>
-      <c r="F3" s="11"/>
+      <c r="F3" s="14"/>
       <c r="I3" s="6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J3" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="11"/>
+      <c r="A4" s="12"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="14"/>
       <c r="D4" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E4" s="2">
         <v>1</v>
       </c>
-      <c r="F4" s="11"/>
+      <c r="F4" s="14"/>
       <c r="I4" s="6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J4" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="11"/>
+      <c r="A5" s="12"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="14"/>
       <c r="D5" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E5" s="2">
         <v>1</v>
       </c>
-      <c r="F5" s="11"/>
+      <c r="F5" s="14"/>
       <c r="I5" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J5" s="6" t="s">
         <v>14</v>
@@ -810,23 +810,23 @@
     </row>
     <row r="6" spans="1:10" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="B6" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="11" t="s">
         <v>8</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E6" s="3">
         <v>4</v>
       </c>
-      <c r="F6" s="12"/>
+      <c r="F6" s="11"/>
       <c r="I6" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="J6" s="6" t="s">
         <v>15</v>
@@ -835,16 +835,16 @@
     <row r="7" spans="1:10" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A7" s="15"/>
       <c r="B7" s="16"/>
-      <c r="C7" s="12"/>
+      <c r="C7" s="11"/>
       <c r="D7" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E7" s="3">
         <v>2</v>
       </c>
-      <c r="F7" s="12"/>
+      <c r="F7" s="11"/>
       <c r="I7" s="6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="J7" s="6" t="s">
         <v>15</v>
@@ -853,82 +853,82 @@
     <row r="8" spans="1:10" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A8" s="15"/>
       <c r="B8" s="16"/>
-      <c r="C8" s="12"/>
+      <c r="C8" s="11"/>
       <c r="D8" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E8" s="3">
         <v>2</v>
       </c>
-      <c r="F8" s="12"/>
+      <c r="F8" s="11"/>
       <c r="I8" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J8" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="D9" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="E9" s="2">
         <v>2</v>
       </c>
-      <c r="F9" s="11"/>
+      <c r="F9" s="14"/>
       <c r="G9"/>
       <c r="H9"/>
       <c r="I9" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="J9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="11"/>
+      <c r="A10" s="12"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="14"/>
       <c r="D10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E10" s="2">
         <v>2</v>
       </c>
-      <c r="F10" s="11"/>
+      <c r="F10" s="14"/>
       <c r="G10"/>
       <c r="H10"/>
       <c r="I10" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="J10" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="11"/>
+      <c r="A11" s="12"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="14"/>
       <c r="D11" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E11" s="2">
         <v>1</v>
       </c>
-      <c r="F11" s="11"/>
+      <c r="F11" s="14"/>
       <c r="G11"/>
       <c r="H11"/>
       <c r="I11" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J11" t="s">
         <v>11</v>
@@ -938,7 +938,7 @@
       <c r="G12"/>
       <c r="H12"/>
       <c r="I12" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="J12" t="s">
         <v>11</v>
@@ -946,7 +946,7 @@
     </row>
     <row r="13" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I13" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="J13" s="6" t="s">
         <v>11</v>
@@ -954,7 +954,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="I14" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="J14" s="6" t="s">
         <v>10</v>
@@ -1047,11 +1047,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="F9:F11"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="B2:B5"/>
     <mergeCell ref="C2:C5"/>
@@ -1059,6 +1054,11 @@
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="B6:B8"/>
     <mergeCell ref="C6:C8"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="F9:F11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1131,7 +1131,7 @@
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="str" cm="1">
         <f t="array" ref="A2:C4">_xlfn.LET(_xlpm.data,_xlfn._xlws.FILTER(BaselineFormations!A:C,(BaselineFormations!A:A&lt;&gt;"Formation")*(NOT(ISBLANK(BaselineFormations!A:A)))),IF(_xlpm.data=0,"",_xlpm.data))</f>
-        <v>Infanterie-Division</v>
+        <v>SX Infanterie-Division</v>
       </c>
       <c r="B2" t="str">
         <v>Infantry</v>
@@ -1166,7 +1166,7 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
-        <v>Leichtes Kavallerie-Brigade</v>
+        <v>SX Leichtes Kavallerie-Brigade</v>
       </c>
       <c r="B3" t="str">
         <v>Cavalry</v>
@@ -1192,7 +1192,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
-        <v>Korps Reservieren</v>
+        <v>SX Korps Reservieren</v>
       </c>
       <c r="B4" t="str">
         <v>Artillery</v>

--- a/assets/ESR Formations-Saxony.xlsx
+++ b/assets/ESR Formations-Saxony.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9EFA18F7C2E81EA4/Documents/NewRecruit/ESR/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="8_{6A81E90A-F6D3-457A-B415-BA9F69045CE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4976F383-EC85-43F2-951F-A3D9E127FBDD}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="8_{6A81E90A-F6D3-457A-B415-BA9F69045CE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{623369B4-7D3D-4DC7-B24A-4631BFC566F4}"/>
   <bookViews>
-    <workbookView xWindow="-27180" yWindow="975" windowWidth="26610" windowHeight="14595" activeTab="1" xr2:uid="{20271C60-C4FB-4B77-A1B3-909BAACA5FD5}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="26610" windowHeight="14595" activeTab="1" xr2:uid="{20271C60-C4FB-4B77-A1B3-909BAACA5FD5}"/>
   </bookViews>
   <sheets>
     <sheet name="BaselineFormations" sheetId="1" r:id="rId1"/>
     <sheet name="ExpandedFormations" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="FromArray_1">_xlfn.ANCHORARRAY(ExpandedFormations!$A$2)</definedName>
-    <definedName name="FromArray_3">_xlfn.ANCHORARRAY(ExpandedFormations!$D$2)</definedName>
+    <definedName name="FromArray_1">_xlfn.ANCHORARRAY(ExpandedFormations!$A$3)</definedName>
+    <definedName name="FromArray_3">_xlfn.ANCHORARRAY(ExpandedFormations!$D$3)</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="44">
   <si>
     <t>Formation</t>
   </si>
@@ -203,6 +203,12 @@
   </si>
   <si>
     <t>SX Korps Reservieren</t>
+  </si>
+  <si>
+    <t>SX Mixed</t>
+  </si>
+  <si>
+    <t>Mixed</t>
   </si>
 </sst>
 </file>
@@ -347,23 +353,23 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -380,6 +386,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -737,34 +747,34 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="14"/>
+      <c r="C2" s="13"/>
       <c r="D2" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="2">
         <v>1</v>
       </c>
-      <c r="F2" s="14"/>
+      <c r="F2" s="13"/>
       <c r="I2" s="5"/>
       <c r="J2" s="5"/>
     </row>
     <row r="3" spans="1:10" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="12"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="14"/>
+      <c r="A3" s="11"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="13"/>
       <c r="D3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E3" s="2">
         <v>6</v>
       </c>
-      <c r="F3" s="14"/>
+      <c r="F3" s="13"/>
       <c r="I3" s="6" t="s">
         <v>27</v>
       </c>
@@ -773,16 +783,16 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="12"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="14"/>
+      <c r="A4" s="11"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="13"/>
       <c r="D4" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E4" s="2">
         <v>1</v>
       </c>
-      <c r="F4" s="14"/>
+      <c r="F4" s="13"/>
       <c r="I4" s="6" t="s">
         <v>28</v>
       </c>
@@ -791,16 +801,16 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="12"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="14"/>
+      <c r="A5" s="11"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="13"/>
       <c r="D5" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E5" s="2">
         <v>1</v>
       </c>
-      <c r="F5" s="14"/>
+      <c r="F5" s="13"/>
       <c r="I5" s="6" t="s">
         <v>29</v>
       </c>
@@ -809,13 +819,13 @@
       </c>
     </row>
     <row r="6" spans="1:10" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="16" t="s">
         <v>8</v>
       </c>
       <c r="D6" s="3" t="s">
@@ -824,7 +834,7 @@
       <c r="E6" s="3">
         <v>4</v>
       </c>
-      <c r="F6" s="11"/>
+      <c r="F6" s="16"/>
       <c r="I6" s="6" t="s">
         <v>30</v>
       </c>
@@ -833,16 +843,16 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="15"/>
-      <c r="B7" s="16"/>
-      <c r="C7" s="11"/>
+      <c r="A7" s="14"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="16"/>
       <c r="D7" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E7" s="3">
         <v>2</v>
       </c>
-      <c r="F7" s="11"/>
+      <c r="F7" s="16"/>
       <c r="I7" s="6" t="s">
         <v>31</v>
       </c>
@@ -851,16 +861,16 @@
       </c>
     </row>
     <row r="8" spans="1:10" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="15"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="11"/>
+      <c r="A8" s="14"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="16"/>
       <c r="D8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E8" s="3">
         <v>2</v>
       </c>
-      <c r="F8" s="11"/>
+      <c r="F8" s="16"/>
       <c r="I8" s="6" t="s">
         <v>32</v>
       </c>
@@ -869,13 +879,13 @@
       </c>
     </row>
     <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="13" t="s">
         <v>24</v>
       </c>
       <c r="D9" s="2" t="s">
@@ -884,7 +894,7 @@
       <c r="E9" s="2">
         <v>2</v>
       </c>
-      <c r="F9" s="14"/>
+      <c r="F9" s="13"/>
       <c r="G9"/>
       <c r="H9"/>
       <c r="I9" t="s">
@@ -895,16 +905,16 @@
       </c>
     </row>
     <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="12"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="14"/>
+      <c r="A10" s="11"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="13"/>
       <c r="D10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E10" s="2">
         <v>2</v>
       </c>
-      <c r="F10" s="14"/>
+      <c r="F10" s="13"/>
       <c r="G10"/>
       <c r="H10"/>
       <c r="I10" t="s">
@@ -915,16 +925,16 @@
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="12"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="14"/>
+      <c r="A11" s="11"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="13"/>
       <c r="D11" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E11" s="2">
         <v>1</v>
       </c>
-      <c r="F11" s="14"/>
+      <c r="F11" s="13"/>
       <c r="G11"/>
       <c r="H11"/>
       <c r="I11" t="s">
@@ -1047,6 +1057,10 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="F9:F11"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="B2:B5"/>
     <mergeCell ref="C2:C5"/>
@@ -1055,10 +1069,6 @@
     <mergeCell ref="B6:B8"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="F6:F8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="F9:F11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1066,7 +1076,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A52F401-E5BC-41DA-8596-65382229DEB1}">
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40.5703125" customWidth="1"/>
@@ -1128,85 +1138,129 @@
         <v>SX Pioniere</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:C4">_xlfn.LET(_xlpm.data,_xlfn._xlws.FILTER(BaselineFormations!A:C,(BaselineFormations!A:A&lt;&gt;"Formation")*(NOT(ISBLANK(BaselineFormations!A:A)))),IF(_xlpm.data=0,"",_xlpm.data))</f>
+    <row r="2" spans="1:15" s="7" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="O2" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" t="str" cm="1">
+        <f t="array" ref="A3:C5">_xlfn.LET(_xlpm.data,_xlfn._xlws.FILTER(BaselineFormations!A:C,(BaselineFormations!A:A&lt;&gt;"Formation")*(NOT(ISBLANK(BaselineFormations!A:A)))),IF(_xlpm.data=0,"",_xlpm.data))</f>
         <v>SX Infanterie-Division</v>
       </c>
-      <c r="B2" t="str">
+      <c r="B3" t="str">
         <v>Infantry</v>
       </c>
-      <c r="C2" t="str">
+      <c r="C3" t="str">
         <v/>
       </c>
-      <c r="D2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
-      <c r="L2" t="s">
-        <v>13</v>
-      </c>
-      <c r="M2" t="s">
-        <v>13</v>
-      </c>
-      <c r="N2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" t="str">
-        <v>SX Leichtes Kavallerie-Brigade</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Cavalry</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Rapid Deployment</v>
-      </c>
-      <c r="H3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M3" t="s">
         <v>13</v>
       </c>
       <c r="N3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
+        <v>SX Leichtes Kavallerie-Brigade</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Cavalry</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Rapid Deployment</v>
+      </c>
+      <c r="H4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K4" t="s">
+        <v>13</v>
+      </c>
+      <c r="N4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" t="str">
         <v>SX Korps Reservieren</v>
       </c>
-      <c r="B4" t="str">
+      <c r="B5" t="str">
         <v>Artillery</v>
       </c>
-      <c r="C4" t="str">
+      <c r="C5" t="str">
         <v>Reinforcements</v>
       </c>
-      <c r="L4" t="s">
-        <v>13</v>
-      </c>
-      <c r="M4" t="s">
-        <v>13</v>
-      </c>
-      <c r="O4" t="s">
+      <c r="L5" t="s">
+        <v>13</v>
+      </c>
+      <c r="M5" t="s">
+        <v>13</v>
+      </c>
+      <c r="O5" t="s">
         <v>13</v>
       </c>
     </row>
